--- a/outputs/DEG着色_フロー整理.xlsx
+++ b/outputs/DEG着色_フロー整理.xlsx
@@ -610,7 +610,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:G15"/>
+  <dimension ref="A1:G17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -679,7 +679,7 @@
         </is>
       </c>
     </row>
-    <row r="4" ht="70" customHeight="1">
+    <row r="4" ht="72" customHeight="1">
       <c r="A4" s="6" t="inlineStr">
         <is>
           <t>残った仮説（本流）</t>
@@ -716,7 +716,7 @@
         </is>
       </c>
     </row>
-    <row r="5" ht="96" customHeight="1">
+    <row r="5" ht="128" customHeight="1">
       <c r="A5" s="8" t="inlineStr">
         <is>
           <t>残した理由（なぜ生き残るか）</t>
@@ -744,7 +744,7 @@
       </c>
       <c r="F5" s="9" t="inlineStr">
         <is>
-          <t>①酸素フリーで進む=酸素で止まる事実(F2)と整合 ②C-1503トップに活性サビ(黒異物・XRF98.5%鉄)実在 ③高pH＋高温が揃う唯一の塔 ④A-ALD自己縮合は共役3-4まで実測(9連結は微量だが微量で色がつく)。</t>
+          <t>①酸素フリーで進む=酸素で止まる事実(F2)と整合 ②C-1503トップに活性サビ(黒異物・XRF98.5%鉄)実在 ③高pH＋高温が揃う唯一の塔 ④A-ALD自己縮合は共役3-4まで実測(9連結は微量だが微量で色がつく) ⑤活性サビはルイス酸点として働き、高pH(塩基)と組んだ酸塩基二元触媒で脱水(発色)を加速。電子移動・酸素を要さずF2と両立し、高pH＋活性サビが揃う唯一塔=C-1503の根拠を強める。</t>
         </is>
       </c>
       <c r="G5" s="9" t="inlineStr">
@@ -753,7 +753,7 @@
         </is>
       </c>
     </row>
-    <row r="6" ht="56" customHeight="1">
+    <row r="6" ht="58" customHeight="1">
       <c r="A6" s="10" t="inlineStr">
         <is>
           <t>落とした仮説</t>
@@ -791,7 +791,7 @@
         </is>
       </c>
     </row>
-    <row r="7" ht="96" customHeight="1">
+    <row r="7" ht="118" customHeight="1">
       <c r="A7" s="12" t="inlineStr">
         <is>
           <t>落とした理由（なぜ消えるか＝事実紐付け）</t>
@@ -820,7 +820,8 @@
       <c r="F7" s="13" t="inlineStr">
         <is>
           <t>ラジカル重合は酸素が開始剤→酸素で止まる事実と逆、鉄サビ単独で着色せず(RD)。
-ルートBはホルム+アセト揃えば成立・検出例ありで否定せずだが450nm直接証拠なし・寄与度不明で要検証。</t>
+ルートBは450nm直接証拠なし・寄与度不明で要検証(否定はせず)。
+※落とすのは『ラジカル開始剤としての鉄』。『ルイス酸触媒としての鉄』は残す(残した理由⑤)。</t>
         </is>
       </c>
       <c r="G7" s="13" t="inlineStr">
@@ -839,12 +840,12 @@
     <row r="10" ht="30" customHeight="1">
       <c r="A10" s="15" t="inlineStr">
         <is>
-          <t>ケースA</t>
+          <t>効き方</t>
         </is>
       </c>
       <c r="B10" s="16" t="inlineStr">
         <is>
-          <t>C-1503でP検出 → DEG塔で金属不活性化（現行説成立）。</t>
+          <t>リン酸鉄被膜が鉄表面サイトを封鎖→鉄の触媒作用を停止。redoxサイクル封じに限定せず、ルイス酸触媒(ルートA加速)としての鉄でも成立しF2と両立。</t>
         </is>
       </c>
       <c r="C10" s="17" t="n"/>
@@ -856,12 +857,12 @@
     <row r="11" ht="30" customHeight="1">
       <c r="A11" s="15" t="inlineStr">
         <is>
-          <t>ケースB</t>
+          <t>ケースA</t>
         </is>
       </c>
       <c r="B11" s="16" t="inlineStr">
         <is>
-          <t>C-1503でP無し → 効いた場所は上流(MEG/C-1502)で前駆体生成抑制（高橋説）。着色現場=DEG塔とテンション。</t>
+          <t>C-1503でP検出 → DEG塔で金属(活性サビ)不活性化＝現行説成立。本線。</t>
         </is>
       </c>
       <c r="C11" s="17" t="n"/>
@@ -873,12 +874,12 @@
     <row r="12" ht="30" customHeight="1">
       <c r="A12" s="15" t="inlineStr">
         <is>
-          <t>決め手</t>
+          <t>ケースB</t>
         </is>
       </c>
       <c r="B12" s="16" t="inlineStr">
         <is>
-          <t>C-1503ミドル充填部の壁面P分析（足場後採取）。</t>
+          <t>C-1503でP無し → 効いた場所は上流(MEG/C-1502)で前駆体生成抑制（高橋説）。着色現場=DEG塔とテンション。</t>
         </is>
       </c>
       <c r="C12" s="17" t="n"/>
@@ -887,36 +888,72 @@
       <c r="F12" s="17" t="n"/>
       <c r="G12" s="17" t="n"/>
     </row>
-    <row r="14" ht="22" customHeight="1">
-      <c r="A14" s="14" t="inlineStr">
+    <row r="13" ht="30" customHeight="1">
+      <c r="A13" s="15" t="inlineStr">
+        <is>
+          <t>決め手①</t>
+        </is>
+      </c>
+      <c r="B13" s="16" t="inlineStr">
+        <is>
+          <t>C-1503ミドル充填部の壁面P分析（足場後採取）。リン入れてMEG-UV効かず=上流説の材料(F8)も突き合わせ。</t>
+        </is>
+      </c>
+      <c r="C13" s="17" t="n"/>
+      <c r="D13" s="17" t="n"/>
+      <c r="E13" s="17" t="n"/>
+      <c r="F13" s="17" t="n"/>
+      <c r="G13" s="17" t="n"/>
+    </row>
+    <row r="14" ht="30" customHeight="1">
+      <c r="A14" s="15" t="inlineStr">
+        <is>
+          <t>決め手②</t>
+        </is>
+      </c>
+      <c r="B14" s="16" t="inlineStr">
+        <is>
+          <t>活性黒サビ有/無で酸素フリー着色速度を比較。加速ならルイス酸触媒を直接証明（redox・酸素から分離）。</t>
+        </is>
+      </c>
+      <c r="C14" s="17" t="n"/>
+      <c r="D14" s="17" t="n"/>
+      <c r="E14" s="17" t="n"/>
+      <c r="F14" s="17" t="n"/>
+      <c r="G14" s="17" t="n"/>
+    </row>
+    <row r="16" ht="22" customHeight="1">
+      <c r="A16" s="14" t="inlineStr">
         <is>
           <t>一本化した筋</t>
         </is>
       </c>
     </row>
-    <row r="15" ht="64" customHeight="1">
-      <c r="A15" s="18" t="inlineStr">
-        <is>
-          <t>原料ALD増 → 大半パージ・一部隠れ形で逃げる → 脱水塔以降で重質化して運搬 → MEG塔系で分解しALDに戻り「湧いて見える」 → C-1503(高pH・高温・活性サビ)でアルドール縮合→共役ポリエナール → タンクで酸素なしに成長 → 450nm着色。
+    <row r="17" ht="64" customHeight="1">
+      <c r="A17" s="18" t="inlineStr">
+        <is>
+          <t>原料ALD増 → 大半パージ・一部隠れ形で逃げる → 脱水塔以降で重質化して運搬 → MEG塔系で分解しALDに戻り「湧いて見える」 → C-1503(高pH・高温・活性サビ＝酸塩基二元触媒)でアルドール縮合→共役ポリエナール → タンクで酸素なしに成長 → 450nm着色。
 動かない軸＝DEGに活性アルデヒドを入れない（IERのガードがなく活性ALDが残ると着色物質に化ける）。</t>
         </is>
       </c>
-      <c r="B15" s="17" t="n"/>
-      <c r="C15" s="17" t="n"/>
-      <c r="D15" s="17" t="n"/>
-      <c r="E15" s="17" t="n"/>
-      <c r="F15" s="17" t="n"/>
-      <c r="G15" s="17" t="n"/>
+      <c r="B17" s="17" t="n"/>
+      <c r="C17" s="17" t="n"/>
+      <c r="D17" s="17" t="n"/>
+      <c r="E17" s="17" t="n"/>
+      <c r="F17" s="17" t="n"/>
+      <c r="G17" s="17" t="n"/>
     </row>
   </sheetData>
-  <mergeCells count="8">
-    <mergeCell ref="A14:G14"/>
+  <mergeCells count="10">
     <mergeCell ref="B10:G10"/>
     <mergeCell ref="A1:G1"/>
+    <mergeCell ref="A17:G17"/>
     <mergeCell ref="A9:G9"/>
+    <mergeCell ref="B14:G14"/>
     <mergeCell ref="A2:G2"/>
+    <mergeCell ref="A16:G16"/>
     <mergeCell ref="B12:G12"/>
-    <mergeCell ref="A15:G15"/>
+    <mergeCell ref="B13:G13"/>
     <mergeCell ref="B11:G11"/>
   </mergeCells>
   <pageMargins left="0.3" right="0.3" top="0.4" bottom="0.4" header="0.5" footer="0.5"/>

--- a/outputs/DEG着色_フロー整理.xlsx
+++ b/outputs/DEG着色_フロー整理.xlsx
@@ -97,7 +97,7 @@
       <sz val="12"/>
     </font>
   </fonts>
-  <fills count="11">
+  <fills count="12">
     <fill>
       <patternFill/>
     </fill>
@@ -149,6 +149,11 @@
         <fgColor rgb="00FFFFFF"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FCE4D6"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="2">
     <border>
@@ -176,7 +181,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="24">
+  <cellXfs count="30">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" indent="1"/>
@@ -223,13 +228,28 @@
     <xf numFmtId="0" fontId="5" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="8" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="9" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="11" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="11" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
     <xf numFmtId="0" fontId="10" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
@@ -244,6 +264,9 @@
     </xf>
     <xf numFmtId="0" fontId="12" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -610,22 +633,22 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:G17"/>
+  <dimension ref="A1:G32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="22" customWidth="1" min="1" max="1"/>
-    <col width="30" customWidth="1" min="2" max="2"/>
-    <col width="30" customWidth="1" min="3" max="3"/>
-    <col width="30" customWidth="1" min="4" max="4"/>
-    <col width="30" customWidth="1" min="5" max="5"/>
-    <col width="30" customWidth="1" min="6" max="6"/>
-    <col width="30" customWidth="1" min="7" max="7"/>
+    <col width="24" customWidth="1" min="1" max="1"/>
+    <col width="32" customWidth="1" min="2" max="2"/>
+    <col width="32" customWidth="1" min="3" max="3"/>
+    <col width="32" customWidth="1" min="4" max="4"/>
+    <col width="32" customWidth="1" min="5" max="5"/>
+    <col width="32" customWidth="1" min="6" max="6"/>
+    <col width="32" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>DEG着色シナリオ　横フロー整理</t>
+          <t>DEG着色シナリオ　横フロー整理（詳細版）</t>
         </is>
       </c>
     </row>
@@ -679,7 +702,7 @@
         </is>
       </c>
     </row>
-    <row r="4" ht="72" customHeight="1">
+    <row r="4" ht="89" customHeight="1">
       <c r="A4" s="6" t="inlineStr">
         <is>
           <t>残った仮説（本流）</t>
@@ -687,36 +710,36 @@
       </c>
       <c r="B4" s="7" t="inlineStr">
         <is>
-          <t>ALD(A/F-ALD)が増加。水が多く遊離のまま。</t>
+          <t>EO反応器でアセトアルデヒド/ホルムアルデヒド(A-ALD/F-ALD)が増加する。系内は水が多く、ALDは反応せず遊離(単体)のまま存在する。</t>
         </is>
       </c>
       <c r="C4" s="7" t="inlineStr">
         <is>
-          <t>大半はパージで系外へ。一部が隠れ形(アセタール等)で逃げ切る。</t>
+          <t>ALDの大半はパージ(系外排出)で抜ける。一部がアセタール等の『隠れ形』に化けてパージをすり抜け、下流へ逃げ切る。</t>
         </is>
       </c>
       <c r="D4" s="7" t="inlineStr">
         <is>
-          <t>アセタール化で重質化し下流まで運ばれる。</t>
+          <t>乾いた(低水分)条件でアセタール化が進み重質化する。重くなった分子として下流まで運ばれる。</t>
         </is>
       </c>
       <c r="E4" s="7" t="inlineStr">
         <is>
-          <t>熱・アルカリで隠れ形が分解しALDに戻る(C-1502付近で湧いて見える)。</t>
+          <t>熱とアルカリで『隠れ形』(アセタール等)が分解し、再びALDに戻る。その結果C-1502付近でALDが『湧いて見える』。</t>
         </is>
       </c>
       <c r="F4" s="7" t="inlineStr">
         <is>
-          <t>高pH＋高温＋活性サビが揃い、アルドール縮合→脱水で共役ポリエナール(300/450nm)。塩基触媒・酸素フリー。</t>
+          <t>高pH＋高温＋活性サビが揃い、ALDのアルドール縮合→脱水が進んで共役ポリエナール(300/450nmの発色体)を生成する。塩基触媒・酸素フリーで進行する。これが着色の本体。</t>
         </is>
       </c>
       <c r="G4" s="7" t="inlineStr">
         <is>
-          <t>残った前駆体が保管中に成長→450nm。塩基触媒で酸素なしに進む(縮合/アクロレインのアニオン重合)。</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="128" customHeight="1">
+          <t>DEG塔で生じた前駆体(短い共役体)がタンク保管中に成長し、450nm発色に至る。塩基触媒のため酸素がなくても進む(アルドール縮合の継続/アクロレインのアニオン重合)。</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="251" customHeight="1">
       <c r="A5" s="8" t="inlineStr">
         <is>
           <t>残した理由（なぜ生き残るか）</t>
@@ -724,36 +747,36 @@
       </c>
       <c r="B5" s="9" t="inlineStr">
         <is>
-          <t>EO触媒劣化で原料ALD増は事実一致。従来も微量(1ppm以下)常在。</t>
+          <t>EO触媒の劣化で原料側のALDが増えるのは観測事実と一致。これらALDは元々微量(1ppm以下)で常在しており、増加分が下流の問題に効いてくる。ここが発生源。</t>
         </is>
       </c>
       <c r="C5" s="9" t="inlineStr">
         <is>
-          <t>A-ALD等はここでパージが通常。原料ALD増で逃げ切る量が増え顕在化、と整合(要検証)。</t>
+          <t>A-ALD等はこの工程で通常パージされる。原料ALD増により『逃げ切る』絶対量が増え、下流で顕在化したと考えれば整合する(要検証)。</t>
         </is>
       </c>
       <c r="D5" s="9" t="inlineStr">
         <is>
-          <t>水が少なくアセタール側に寄る。重質化すれば届く。</t>
+          <t>水が少ないと平衡がアセタール側に寄る。重質化すれば揮発しにくくなり、蒸留系を越えてDEG側まで届く。</t>
         </is>
       </c>
       <c r="E5" s="9" t="inlineStr">
         <is>
-          <t>バランス上C-1502付近でA/F-ALDが生成するように見える(C-1501ボトムは過去同水準=MEG塔単独生成でない)。隠れ形分解で説明可。</t>
+          <t>物質収支上C-1502付近でA/F-ALDが生成しているように見える(F9)。C-1501ボトムは過去と同水準＝MEG塔そのものが新規生成源ではなく、隠れ形の分解戻りで説明できる。</t>
         </is>
       </c>
       <c r="F5" s="9" t="inlineStr">
         <is>
-          <t>①酸素フリーで進む=酸素で止まる事実(F2)と整合 ②C-1503トップに活性サビ(黒異物・XRF98.5%鉄)実在 ③高pH＋高温が揃う唯一の塔 ④A-ALD自己縮合は共役3-4まで実測(9連結は微量だが微量で色がつく) ⑤活性サビはルイス酸点として働き、高pH(塩基)と組んだ酸塩基二元触媒で脱水(発色)を加速。電子移動・酸素を要さずF2と両立し、高pH＋活性サビが揃う唯一塔=C-1503の根拠を強める。</t>
+          <t>①酸素フリーで進む＝酸素で悪化が止まる事実(F2)と整合。②C-1503トップに活性サビ(黒異物・XRF98.5%鉄)が実在(F4)。③高pH＋高温が揃う唯一の塔。④A-ALDの自己縮合は共役3-4まで実測(F6)。9連結は微量だが、微量でも色はつく。⑤活性サビはルイス酸点として働き、高pH(塩基)と組んだ酸塩基二元触媒として脱水(＝発色)を加速し得る。電子移動も酸素も要さないためF2と両立し、『高pH＋活性サビが揃う唯一塔＝C-1503でのみ進む』理由を与える。F5(サビ単独では着色せず)とも整合(触媒であって単独原因ではない)。</t>
         </is>
       </c>
       <c r="G5" s="9" t="inlineStr">
         <is>
-          <t>本管DEGは27日でAPHA5以下・無変質、タンク品で450成長=成長はタンク(滞留)で起きる。N2・遮光でも進行=酸素不要。塩基触媒経路は酸素フリー。</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="58" customHeight="1">
+          <t>本管DEGは27日でもAPHA5以下・無変質なのに、タンク品で450が成長する(F7)＝成長はタンク(滞留)で起きる。N2・遮光下でも進行する＝酸素は不要。塩基触媒経路は本質的に酸素フリー。</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="89" customHeight="1">
       <c r="A6" s="10" t="inlineStr">
         <is>
           <t>落とした仮説</t>
@@ -761,37 +784,37 @@
       </c>
       <c r="B6" s="11" t="inlineStr">
         <is>
-          <t>（なし）</t>
+          <t>（明確な対立仮説はなし。発生源としてほぼ確定。）</t>
         </is>
       </c>
       <c r="C6" s="11" t="inlineStr">
         <is>
-          <t>「全量パージされ下流に来ない」を否定。</t>
+          <t>『ALDは全量パージされ下流には来ない』という見方。</t>
         </is>
       </c>
       <c r="D6" s="11" t="inlineStr">
         <is>
-          <t>× 軽質ALDのままDEGへ抜ける。</t>
+          <t>軽質ALDのまま(重質化せず)DEG塔へ抜けるという見方。</t>
         </is>
       </c>
       <c r="E6" s="11" t="inlineStr">
         <is>
-          <t>× MEG塔そのものが着色の場。</t>
+          <t>MEG塔(C-1501/1502)そのものが着色の発生現場であるという見方。</t>
         </is>
       </c>
       <c r="F6" s="11" t="inlineStr">
         <is>
-          <t>× 鉄＋酸素のラジカル重合が主役。
-△ ルートB(F+A交差→アクロレイン)は残す(要検証)。</t>
+          <t>①× 鉄＋酸素のラジカル重合が主役、という見方。
+②△ ルートB(F-ALD＋A-ALDの交差→アクロレイン経由)。完全否定はせず要検証として残す。</t>
         </is>
       </c>
       <c r="G6" s="11" t="inlineStr">
         <is>
-          <t>× タンクでラジカル重合して着色。</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="118" customHeight="1">
+          <t>タンク内でラジカル重合して着色する、という見方。</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="183.5" customHeight="1">
       <c r="A7" s="12" t="inlineStr">
         <is>
           <t>落とした理由（なぜ消えるか＝事実紐付け）</t>
@@ -804,29 +827,28 @@
       </c>
       <c r="C7" s="13" t="inlineStr">
         <is>
-          <t>実際に下流でALDが見えている。</t>
+          <t>実際に下流(MEG塔・DEG塔)でALDが検出されており、全量パージは事実に反する。一定量が必ず通り抜けている。</t>
         </is>
       </c>
       <c r="D7" s="13" t="inlineStr">
         <is>
-          <t>軽質ALDは物性上そのままDEGに来ない(高橋)。運ぶには重質化が必要。</t>
+          <t>軽質ALDは物性上そのままではDEGに来ない(高橋)。DEGまで運ぶには一度重質化する必要がある(F10)。</t>
         </is>
       </c>
       <c r="E7" s="13" t="inlineStr">
         <is>
-          <t>C-1501/1502開放(6/12)→サビ・汚れなし。触媒(活性サビ)の場でない。</t>
+          <t>C-1501/1502を開放点検(6/12)した結果、サビ・汚れがなかった(F4)。触媒となる活性サビが無く、着色の場ではない。</t>
         </is>
       </c>
       <c r="F7" s="13" t="inlineStr">
         <is>
-          <t>ラジカル重合は酸素が開始剤→酸素で止まる事実と逆、鉄サビ単独で着色せず(RD)。
-ルートBは450nm直接証拠なし・寄与度不明で要検証(否定はせず)。
-※落とすのは『ラジカル開始剤としての鉄』。『ルイス酸触媒としての鉄』は残す(残した理由⑤)。</t>
+          <t>①ラジカル重合は酸素が開始剤だが、F2(酸素で悪化が止まる)と真逆。鉄サビ単独でも着色しない(F5/RD)。よって主役ではない。ただし落とすのは『ラジカル開始剤としての鉄』であり、『ルイス酸触媒としての鉄』(残した理由⑤)は残す。
+②ルートBはホルム＋アセトが揃えば成立し検出例もあるため否定はしないが、450nmへの直接証拠がなく寄与度も不明なため要検証。</t>
         </is>
       </c>
       <c r="G7" s="13" t="inlineStr">
         <is>
-          <t>酸素雰囲気(船・ローリー)で悪化が止まる事実と逆(ラジカル重合は酸素が開始剤)。</t>
+          <t>船・ローリーの酸素雰囲気でむしろ悪化が止まる(F2)。ラジカル重合は酸素が開始剤なので、これと真逆＝タンクのラジカル重合は主役ではない。</t>
         </is>
       </c>
     </row>
@@ -837,7 +859,7 @@
         </is>
       </c>
     </row>
-    <row r="10" ht="30" customHeight="1">
+    <row r="10" ht="37" customHeight="1">
       <c r="A10" s="15" t="inlineStr">
         <is>
           <t>効き方</t>
@@ -845,7 +867,7 @@
       </c>
       <c r="B10" s="16" t="inlineStr">
         <is>
-          <t>リン酸鉄被膜が鉄表面サイトを封鎖→鉄の触媒作用を停止。redoxサイクル封じに限定せず、ルイス酸触媒(ルートA加速)としての鉄でも成立しF2と両立。</t>
+          <t>リン酸鉄被膜が鉄表面サイトを封鎖し、鉄の触媒作用を停止させる。これはFe²⁺⇄Fe³⁺のredoxサイクル封じに限定されず、ルイス酸触媒(ルートA加速)としての鉄でも同じく成立する。どちらの役割でも被膜で潰れるため、F2(酸素で止まる)と両立した形で『リン酸が効いた』を説明できる。</t>
         </is>
       </c>
       <c r="C10" s="17" t="n"/>
@@ -854,7 +876,7 @@
       <c r="F10" s="17" t="n"/>
       <c r="G10" s="17" t="n"/>
     </row>
-    <row r="11" ht="30" customHeight="1">
+    <row r="11" ht="28" customHeight="1">
       <c r="A11" s="15" t="inlineStr">
         <is>
           <t>ケースA</t>
@@ -862,7 +884,7 @@
       </c>
       <c r="B11" s="16" t="inlineStr">
         <is>
-          <t>C-1503でP検出 → DEG塔で金属(活性サビ)不活性化＝現行説成立。本線。</t>
+          <t>C-1503でP検出 → DEG塔で金属(活性サビ)を不活性化＝現行説が成立。これを本線とする。</t>
         </is>
       </c>
       <c r="C11" s="17" t="n"/>
@@ -871,7 +893,7 @@
       <c r="F11" s="17" t="n"/>
       <c r="G11" s="17" t="n"/>
     </row>
-    <row r="12" ht="30" customHeight="1">
+    <row r="12" ht="28" customHeight="1">
       <c r="A12" s="15" t="inlineStr">
         <is>
           <t>ケースB</t>
@@ -879,7 +901,7 @@
       </c>
       <c r="B12" s="16" t="inlineStr">
         <is>
-          <t>C-1503でP無し → 効いた場所は上流(MEG/C-1502)で前駆体生成抑制（高橋説）。着色現場=DEG塔とテンション。</t>
+          <t>C-1503でP無し → 効いた場所は上流(MEG/C-1502)で前駆体の生成を抑えた(高橋説)。この場合『着色現場＝DEG塔』とテンションが残る。</t>
         </is>
       </c>
       <c r="C12" s="17" t="n"/>
@@ -888,7 +910,7 @@
       <c r="F12" s="17" t="n"/>
       <c r="G12" s="17" t="n"/>
     </row>
-    <row r="13" ht="30" customHeight="1">
+    <row r="13" ht="28" customHeight="1">
       <c r="A13" s="15" t="inlineStr">
         <is>
           <t>決め手①</t>
@@ -896,7 +918,7 @@
       </c>
       <c r="B13" s="16" t="inlineStr">
         <is>
-          <t>C-1503ミドル充填部の壁面P分析（足場後採取）。リン入れてMEG-UV効かず=上流説の材料(F8)も突き合わせ。</t>
+          <t>C-1503ミドル充填部の壁面P分析(足場設置後に採取)。あわせて『リンを入れてもMEG-UVは効かず＝上流説の材料(F8)』とも突き合わせる。</t>
         </is>
       </c>
       <c r="C13" s="17" t="n"/>
@@ -905,7 +927,7 @@
       <c r="F13" s="17" t="n"/>
       <c r="G13" s="17" t="n"/>
     </row>
-    <row r="14" ht="30" customHeight="1">
+    <row r="14" ht="28" customHeight="1">
       <c r="A14" s="15" t="inlineStr">
         <is>
           <t>決め手②</t>
@@ -913,7 +935,7 @@
       </c>
       <c r="B14" s="16" t="inlineStr">
         <is>
-          <t>活性黒サビ有/無で酸素フリー着色速度を比較。加速ならルイス酸触媒を直接証明（redox・酸素から分離）。</t>
+          <t>活性黒サビ有/無で酸素フリー条件の着色速度を比較。サビ有で酸素なしでも加速すれば、ルイス酸触媒であることをredox・酸素から分離して直接証明できる(後述『鉄の2つの顔』)。</t>
         </is>
       </c>
       <c r="C14" s="17" t="n"/>
@@ -929,11 +951,11 @@
         </is>
       </c>
     </row>
-    <row r="17" ht="64" customHeight="1">
+    <row r="17" ht="53.5" customHeight="1">
       <c r="A17" s="18" t="inlineStr">
         <is>
-          <t>原料ALD増 → 大半パージ・一部隠れ形で逃げる → 脱水塔以降で重質化して運搬 → MEG塔系で分解しALDに戻り「湧いて見える」 → C-1503(高pH・高温・活性サビ＝酸塩基二元触媒)でアルドール縮合→共役ポリエナール → タンクで酸素なしに成長 → 450nm着色。
-動かない軸＝DEGに活性アルデヒドを入れない（IERのガードがなく活性ALDが残ると着色物質に化ける）。</t>
+          <t>原料ALD増 → 大半はパージ・一部が隠れ形で逃げる → 脱水塔以降で重質化して運搬 → MEG塔系で隠れ形が分解しALDに戻り『湧いて見える』 → C-1503(高pH・高温・活性サビ＝酸塩基二元触媒)でアルドール縮合→脱水で共役ポリエナール → タンクで酸素なしに成長 → 450nm着色。
+動かない軸＝DEGに活性アルデヒドを入れないこと。IER(イオン交換樹脂)のガードがなく活性ALDが残ると、下流で着色物質に化ける。</t>
         </is>
       </c>
       <c r="B17" s="17" t="n"/>
@@ -943,17 +965,233 @@
       <c r="F17" s="17" t="n"/>
       <c r="G17" s="17" t="n"/>
     </row>
+    <row r="19" ht="22" customHeight="1">
+      <c r="A19" s="14" t="inlineStr">
+        <is>
+          <t>機構の確定事項（理由欄の裏付け）</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="28" customHeight="1">
+      <c r="A20" s="19" t="inlineStr">
+        <is>
+          <t>①塩基触媒の再生</t>
+        </is>
+      </c>
+      <c r="B20" s="16" t="inlineStr">
+        <is>
+          <t>NaOHはOH⁻(塩基)として触媒的に働き再生する。アルドールの付加も脱水も塩基触媒で進み、脱水は加熱を要する。したがって高pH＋高温が揃うDEG塔(C-1503)が着色の現場になる。</t>
+        </is>
+      </c>
+      <c r="C20" s="17" t="n"/>
+      <c r="D20" s="17" t="n"/>
+      <c r="E20" s="17" t="n"/>
+      <c r="F20" s="17" t="n"/>
+      <c r="G20" s="17" t="n"/>
+    </row>
+    <row r="21" ht="37" customHeight="1">
+      <c r="A21" s="19" t="inlineStr">
+        <is>
+          <t>②アクロレイン重合の2モード</t>
+        </is>
+      </c>
+      <c r="B21" s="16" t="inlineStr">
+        <is>
+          <t>①アニオン重合：NaOH等の塩基・鉱酸が開始、カルボニル中心、可溶＝液が着色する。②ラジカル重合：金属・酸素・熱・過酸化物が開始、ビニル中心、不溶＝黒い固形になる。NaOHはアニオンの開始剤でありラジカルの開始剤ではない(平尾指摘が正しい)。</t>
+        </is>
+      </c>
+      <c r="C21" s="17" t="n"/>
+      <c r="D21" s="17" t="n"/>
+      <c r="E21" s="17" t="n"/>
+      <c r="F21" s="17" t="n"/>
+      <c r="G21" s="17" t="n"/>
+    </row>
+    <row r="22" ht="28" customHeight="1">
+      <c r="A22" s="19" t="inlineStr">
+        <is>
+          <t>③F2による絞り込み(背骨)</t>
+        </is>
+      </c>
+      <c r="B22" s="16" t="inlineStr">
+        <is>
+          <t>酸素雰囲気で悪化が止まる→ラジカル重合(酸素が開始剤)は主役ではない。主役は酸素フリーの塩基触媒経路で、酸素はむしろ停止側に働く。これが今回の論理の背骨。</t>
+        </is>
+      </c>
+      <c r="C22" s="17" t="n"/>
+      <c r="D22" s="17" t="n"/>
+      <c r="E22" s="17" t="n"/>
+      <c r="F22" s="17" t="n"/>
+      <c r="G22" s="17" t="n"/>
+    </row>
+    <row r="23" ht="37" customHeight="1">
+      <c r="A23" s="19" t="inlineStr">
+        <is>
+          <t>④鉄の関与の正体</t>
+        </is>
+      </c>
+      <c r="B23" s="16" t="inlineStr">
+        <is>
+          <t>鉄は液中Fenton(•OH)ではなく、固体サビ表面の局所活性点として働く。ラジカル源も過酸化水素ではなく、グリコール/エナール/ALDの自動酸化で生じるROOHを鉄がdrier(乾燥剤)型に分解する形。ただし③よりラジカル経路自体は主役ではない。</t>
+        </is>
+      </c>
+      <c r="C23" s="17" t="n"/>
+      <c r="D23" s="17" t="n"/>
+      <c r="E23" s="17" t="n"/>
+      <c r="F23" s="17" t="n"/>
+      <c r="G23" s="17" t="n"/>
+    </row>
+    <row r="24" ht="37" customHeight="1">
+      <c r="A24" s="19" t="inlineStr">
+        <is>
+          <t>⑤立体障害論の検証</t>
+        </is>
+      </c>
+      <c r="B24" s="16" t="inlineStr">
+        <is>
+          <t>『9連結は立体障害でほぼ起きない』(木村)は言い過ぎ。鎖伸長はエナール末端＋小さいA-ALDで進むため立体障害が効きにくく、共役3-4は実測済み(F6)。9連結が微量なのは事実だが『起きない』ではなく『微量でも色がつく』。木村はルートB主役化でルートAを過小評価しており、実際は両ルートが並走する。</t>
+        </is>
+      </c>
+      <c r="C24" s="17" t="n"/>
+      <c r="D24" s="17" t="n"/>
+      <c r="E24" s="17" t="n"/>
+      <c r="F24" s="17" t="n"/>
+      <c r="G24" s="17" t="n"/>
+    </row>
+    <row r="25" ht="37" customHeight="1">
+      <c r="A25" s="19" t="inlineStr">
+        <is>
+          <t>⑥リン酸の作用機構</t>
+        </is>
+      </c>
+      <c r="B25" s="16" t="inlineStr">
+        <is>
+          <t>リン酸鉄被膜がFe²⁺⇄Fe³⁺サイクル(および表面活性点)を封じる。中性〜弱アルカリの水洗では落ちない。赤サビ＝リン被膜(不活性)/黒サビ＝活性。判定はC-1503壁面の目視(赤/黒)＋XRF(P)。効き場所はC-1501/1502/1503のどこかまで絞れるが未確定。リンを入れてもMEG-UVは効かず→上流説の材料でもある(F8)。</t>
+        </is>
+      </c>
+      <c r="C25" s="17" t="n"/>
+      <c r="D25" s="17" t="n"/>
+      <c r="E25" s="17" t="n"/>
+      <c r="F25" s="17" t="n"/>
+      <c r="G25" s="17" t="n"/>
+    </row>
+    <row r="27" ht="22" customHeight="1">
+      <c r="A27" s="14" t="inlineStr">
+        <is>
+          <t>鉄の役割＝2つの顔（今回の深掘り）</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="37" customHeight="1">
+      <c r="A28" s="20" t="inlineStr">
+        <is>
+          <t>ルイス酸触媒として
+【残す ○】</t>
+        </is>
+      </c>
+      <c r="B28" s="21" t="inlineStr">
+        <is>
+          <t>Fe³⁺がルイス酸点としてカルボニルを活性化し、高pH(塩基)と組んで酸塩基二元触媒となる。アルドール縮合・脱水(＝発色)を加速し得る。電子移動も酸素も不要なのでF2と両立する。これが『高pH＋活性サビが揃う唯一塔＝C-1503でのみ進む』理由を与え、F5(サビ単独では着色せず＝触媒であって単独原因でない)とも整合する。</t>
+        </is>
+      </c>
+      <c r="C28" s="17" t="n"/>
+      <c r="D28" s="17" t="n"/>
+      <c r="E28" s="17" t="n"/>
+      <c r="F28" s="17" t="n"/>
+      <c r="G28" s="17" t="n"/>
+    </row>
+    <row r="29" ht="28" customHeight="1">
+      <c r="A29" s="22" t="inlineStr">
+        <is>
+          <t>ラジカル開始剤として
+【落とす ×】</t>
+        </is>
+      </c>
+      <c r="B29" s="23" t="inlineStr">
+        <is>
+          <t>鉄＋酸素＋過酸化物でラジカルを開始し、ビニル重合(不溶の黒固形)を起こす役割。だが酸素が開始剤であるためF2(酸素で止まる)と真逆になる。よってこの役割は主役から外す。</t>
+        </is>
+      </c>
+      <c r="C29" s="17" t="n"/>
+      <c r="D29" s="17" t="n"/>
+      <c r="E29" s="17" t="n"/>
+      <c r="F29" s="17" t="n"/>
+      <c r="G29" s="17" t="n"/>
+    </row>
+    <row r="30" ht="37" customHeight="1">
+      <c r="A30" s="15" t="inlineStr">
+        <is>
+          <t>リン酸との接続</t>
+        </is>
+      </c>
+      <c r="B30" s="16" t="inlineStr">
+        <is>
+          <t>リン酸鉄被膜は鉄表面を物理的に覆い、redox点でもルイス酸点でも同時に潰す。だから『リン酸が効いた』事実は、鉄の役割がredox/ルイス酸のどちらでも説明可能であり、リン酸の効きだけでは2役を判別できない。</t>
+        </is>
+      </c>
+      <c r="C30" s="17" t="n"/>
+      <c r="D30" s="17" t="n"/>
+      <c r="E30" s="17" t="n"/>
+      <c r="F30" s="17" t="n"/>
+      <c r="G30" s="17" t="n"/>
+    </row>
+    <row r="31" ht="28" customHeight="1">
+      <c r="A31" s="15" t="inlineStr">
+        <is>
+          <t>留保（未確定）</t>
+        </is>
+      </c>
+      <c r="B31" s="16" t="inlineStr">
+        <is>
+          <t>ルイス酸触媒として効いている直接証拠はまだ無い。活性サビのルイス酸性(Fe³⁺サイト量)は未測定。あくまで『F2と両立する形で鉄を筋に残せる』という整合性の主張に留まる。</t>
+        </is>
+      </c>
+      <c r="C31" s="17" t="n"/>
+      <c r="D31" s="17" t="n"/>
+      <c r="E31" s="17" t="n"/>
+      <c r="F31" s="17" t="n"/>
+      <c r="G31" s="17" t="n"/>
+    </row>
+    <row r="32" ht="37" customHeight="1">
+      <c r="A32" s="15" t="inlineStr">
+        <is>
+          <t>切り分け試験</t>
+        </is>
+      </c>
+      <c r="B32" s="16" t="inlineStr">
+        <is>
+          <t>前駆体(活性ALD)＋塩基＋熱を、酸素フリー条件で『活性黒サビ有/無』で着色速度比較する。サビ有で酸素なしでも加速すれば、ルイス酸触媒であることをラジカル/酸素から完全に分離して証明できる。F5の『サビ単独』とは別物で、サビ＋基質＋塩基で見るのが正しい。</t>
+        </is>
+      </c>
+      <c r="C32" s="17" t="n"/>
+      <c r="D32" s="17" t="n"/>
+      <c r="E32" s="17" t="n"/>
+      <c r="F32" s="17" t="n"/>
+      <c r="G32" s="17" t="n"/>
+    </row>
   </sheetData>
-  <mergeCells count="10">
+  <mergeCells count="23">
+    <mergeCell ref="A17:G17"/>
+    <mergeCell ref="B14:G14"/>
+    <mergeCell ref="B23:G23"/>
+    <mergeCell ref="B13:G13"/>
+    <mergeCell ref="A19:G19"/>
+    <mergeCell ref="B29:G29"/>
     <mergeCell ref="B10:G10"/>
+    <mergeCell ref="B28:G28"/>
+    <mergeCell ref="A9:G9"/>
+    <mergeCell ref="B30:G30"/>
+    <mergeCell ref="B24:G24"/>
+    <mergeCell ref="B20:G20"/>
     <mergeCell ref="A1:G1"/>
-    <mergeCell ref="A17:G17"/>
-    <mergeCell ref="A9:G9"/>
-    <mergeCell ref="B14:G14"/>
+    <mergeCell ref="B32:G32"/>
+    <mergeCell ref="A16:G16"/>
+    <mergeCell ref="B25:G25"/>
+    <mergeCell ref="B22:G22"/>
+    <mergeCell ref="A27:G27"/>
+    <mergeCell ref="B31:G31"/>
     <mergeCell ref="A2:G2"/>
-    <mergeCell ref="A16:G16"/>
     <mergeCell ref="B12:G12"/>
-    <mergeCell ref="B13:G13"/>
+    <mergeCell ref="B21:G21"/>
     <mergeCell ref="B11:G11"/>
   </mergeCells>
   <pageMargins left="0.3" right="0.3" top="0.4" bottom="0.4" header="0.5" footer="0.5"/>
@@ -970,189 +1208,189 @@
   <dimension ref="A1:B17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="16" customWidth="1" min="1" max="1"/>
-    <col width="90" customWidth="1" min="2" max="2"/>
+    <col width="18" customWidth="1" min="1" max="1"/>
+    <col width="95" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
     <row r="1" ht="28" customHeight="1">
-      <c r="A1" s="19" t="inlineStr">
+      <c r="A1" s="24" t="inlineStr">
         <is>
           <t>確認された事実（F番号）</t>
         </is>
       </c>
     </row>
-    <row r="2" ht="30" customHeight="1">
-      <c r="A2" s="20" t="inlineStr">
+    <row r="2" ht="28" customHeight="1">
+      <c r="A2" s="25" t="inlineStr">
         <is>
           <t>F1</t>
         </is>
       </c>
-      <c r="B2" s="21" t="inlineStr">
-        <is>
-          <t>採取直後無色、保管中(タンク)に着色進行。</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="30" customHeight="1">
-      <c r="A3" s="20" t="inlineStr">
+      <c r="B2" s="26" t="inlineStr">
+        <is>
+          <t>採取直後は無色、保管中(タンク)に着色が進行する。</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="28" customHeight="1">
+      <c r="A3" s="25" t="inlineStr">
         <is>
           <t>F2</t>
         </is>
       </c>
-      <c r="B3" s="22" t="inlineStr">
-        <is>
-          <t>酸素雰囲気(船・ローリー)で悪化が止まる。N2・遮光でも進行。【最重要絞り込み】</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="30" customHeight="1">
-      <c r="A4" s="20" t="inlineStr">
+      <c r="B3" s="27" t="inlineStr">
+        <is>
+          <t>酸素雰囲気(船・ローリー)で悪化が止まる。N2・遮光でも進行する。【最重要絞り込み】</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="28" customHeight="1">
+      <c r="A4" s="25" t="inlineStr">
         <is>
           <t>F3</t>
         </is>
       </c>
-      <c r="B4" s="21" t="inlineStr">
-        <is>
-          <t>300＋450nm=長い共役系(ポリエナール)。</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="30" customHeight="1">
-      <c r="A5" s="20" t="inlineStr">
+      <c r="B4" s="26" t="inlineStr">
+        <is>
+          <t>300＋450nm＝長い共役系(ポリエナール)の吸収。</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="38" customHeight="1">
+      <c r="A5" s="25" t="inlineStr">
         <is>
           <t>F4</t>
         </is>
       </c>
-      <c r="B5" s="21" t="inlineStr">
-        <is>
-          <t>C-1503トップに黒異物・サビ(XRF98.5%鉄)。C-1501/1502はサビ・汚れなし(6/12)。</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="30" customHeight="1">
-      <c r="A6" s="20" t="inlineStr">
+      <c r="B5" s="26" t="inlineStr">
+        <is>
+          <t>C-1503トップに黒異物・サビ(XRF98.5%鉄)。C-1501/1502はサビ・汚れなし(6/12開放)。</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="28" customHeight="1">
+      <c r="A6" s="25" t="inlineStr">
         <is>
           <t>F5</t>
         </is>
       </c>
-      <c r="B6" s="21" t="inlineStr">
-        <is>
-          <t>鉄サビ単独では着色せず(RD保管・蒸留試験)。</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="30" customHeight="1">
-      <c r="A7" s="20" t="inlineStr">
+      <c r="B6" s="26" t="inlineStr">
+        <is>
+          <t>鉄サビ単独では着色しない(RD保管・蒸留試験)。</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="28" customHeight="1">
+      <c r="A7" s="25" t="inlineStr">
         <is>
           <t>F6</t>
         </is>
       </c>
-      <c r="B7" s="21" t="inlineStr">
-        <is>
-          <t>A-ALD縮合は共役3-4まで実測。9連結は微量だが微量で色がつく。</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="30" customHeight="1">
-      <c r="A8" s="20" t="inlineStr">
+      <c r="B7" s="26" t="inlineStr">
+        <is>
+          <t>A-ALD縮合は共役3-4まで実測。9連結は微量だが、微量でも色がつく。</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="28" customHeight="1">
+      <c r="A8" s="25" t="inlineStr">
         <is>
           <t>F7</t>
         </is>
       </c>
-      <c r="B8" s="21" t="inlineStr">
-        <is>
-          <t>本管DEG27日でAPHA5以下・無変質、タンク品で450成長。</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="30" customHeight="1">
-      <c r="A9" s="20" t="inlineStr">
+      <c r="B8" s="26" t="inlineStr">
+        <is>
+          <t>本管DEGは27日でAPHA5以下・無変質、タンク品で450が成長する。</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="28" customHeight="1">
+      <c r="A9" s="25" t="inlineStr">
         <is>
           <t>F8</t>
         </is>
       </c>
-      <c r="B9" s="21" t="inlineStr">
-        <is>
-          <t>着色に効いたのはリン酸のみ。ただしリン入れてもMEG-UV効かず。</t>
-        </is>
-      </c>
-    </row>
-    <row r="10" ht="30" customHeight="1">
-      <c r="A10" s="20" t="inlineStr">
+      <c r="B9" s="26" t="inlineStr">
+        <is>
+          <t>着色に効いたのはリン酸のみ。ただしリンを入れてもMEG-UVは効かず。</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="28" customHeight="1">
+      <c r="A10" s="25" t="inlineStr">
         <is>
           <t>F9</t>
         </is>
       </c>
-      <c r="B10" s="21" t="inlineStr">
-        <is>
-          <t>バランス上C-1502付近でALD生成に見える。C-1501ボトムは過去同水準。</t>
-        </is>
-      </c>
-    </row>
-    <row r="11" ht="30" customHeight="1">
-      <c r="A11" s="20" t="inlineStr">
+      <c r="B10" s="26" t="inlineStr">
+        <is>
+          <t>物質収支上C-1502付近でALD生成に見える。C-1501ボトムは過去同水準。</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="28" customHeight="1">
+      <c r="A11" s="25" t="inlineStr">
         <is>
           <t>F10</t>
         </is>
       </c>
-      <c r="B11" s="21" t="inlineStr">
-        <is>
-          <t>軽質ALDは物性上そのままDEGに来ない(高橋)。運ぶには重質化必要。</t>
+      <c r="B11" s="26" t="inlineStr">
+        <is>
+          <t>軽質ALDは物性上そのままDEGに来ない(高橋)。運ぶには重質化が必要。</t>
         </is>
       </c>
     </row>
     <row r="13" ht="24" customHeight="1">
-      <c r="A13" s="23" t="inlineStr">
+      <c r="A13" s="28" t="inlineStr">
         <is>
           <t>塔ごとの場所事実（追記枠）</t>
         </is>
       </c>
     </row>
-    <row r="14" ht="30" customHeight="1">
+    <row r="14" ht="28" customHeight="1">
       <c r="A14" s="15" t="inlineStr">
         <is>
           <t>C-1501/1502</t>
         </is>
       </c>
-      <c r="B14" s="16" t="inlineStr">
-        <is>
-          <t>開放(6/12)でサビ・汚れなし。活性サビの場でない＝着色の場ではない。</t>
-        </is>
-      </c>
-    </row>
-    <row r="15" ht="30" customHeight="1">
+      <c r="B14" s="29" t="inlineStr">
+        <is>
+          <t>開放(6/12)でサビ・汚れなし。活性サビの場ではない＝着色の場ではない。</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="28" customHeight="1">
       <c r="A15" s="15" t="inlineStr">
         <is>
           <t>C-1503トップ</t>
         </is>
       </c>
-      <c r="B15" s="16" t="inlineStr">
-        <is>
-          <t>黒異物・活性サビ(XRF98.5%鉄)実在。高pH＋高温が揃う唯一の塔＝着色の本体。</t>
-        </is>
-      </c>
-    </row>
-    <row r="16" ht="30" customHeight="1">
+      <c r="B15" s="29" t="inlineStr">
+        <is>
+          <t>黒異物・活性サビ(XRF98.5%鉄)が実在。高pH＋高温が揃う唯一の塔＝着色の本体。</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="28" customHeight="1">
       <c r="A16" s="15" t="inlineStr">
         <is>
           <t>C-1503ミドル充填部</t>
         </is>
       </c>
-      <c r="B16" s="16" t="inlineStr">
-        <is>
-          <t>壁面P分析を足場後に採取予定（リン酸の効き場所の決め手）。</t>
-        </is>
-      </c>
-    </row>
-    <row r="17" ht="30" customHeight="1">
+      <c r="B16" s="29" t="inlineStr">
+        <is>
+          <t>壁面P分析を足場設置後に採取予定(リン酸の効き場所の決め手①)。</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="28" customHeight="1">
       <c r="A17" s="15" t="inlineStr">
         <is>
           <t>製品タンク</t>
         </is>
       </c>
-      <c r="B17" s="16" t="inlineStr">
-        <is>
-          <t>滞留で450nm成長。N2・遮光でも進行＝酸素不要（塩基触媒経路）。</t>
+      <c r="B17" s="29" t="inlineStr">
+        <is>
+          <t>滞留で450nmが成長。N2・遮光でも進行＝酸素不要(塩基触媒経路)。</t>
         </is>
       </c>
     </row>
